--- a/Database_ChefIA.xlsx
+++ b/Database_ChefIA.xlsx
@@ -418,7 +418,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M3"/>
+  <dimension ref="A1:M7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -469,7 +469,7 @@
       </c>
       <c r="J1" t="inlineStr">
         <is>
-          <t>insumos_en_stock</t>
+          <t>insumos_disponibles</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">
@@ -567,7 +567,11 @@
       <c r="I3" t="n">
         <v>1</v>
       </c>
-      <c r="J3" t="inlineStr"/>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>3,9,12,1</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr">
         <is>
           <t>Equilibrada</t>
@@ -577,6 +581,184 @@
       <c r="M3" t="n">
         <v>34</v>
       </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>prueba</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>25</v>
+      </c>
+      <c r="E4" t="n">
+        <v>85</v>
+      </c>
+      <c r="F4" t="n">
+        <v>186</v>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Sierra</t>
+        </is>
+      </c>
+      <c r="H4" t="n">
+        <v>15</v>
+      </c>
+      <c r="I4" t="n">
+        <v>5</v>
+      </c>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Equilibrada</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>andres</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>25</v>
+      </c>
+      <c r="E5" t="n">
+        <v>85</v>
+      </c>
+      <c r="F5" t="n">
+        <v>170</v>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Costa</t>
+        </is>
+      </c>
+      <c r="H5" t="n">
+        <v>10</v>
+      </c>
+      <c r="I5" t="n">
+        <v>1</v>
+      </c>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Equilibrada</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="n">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>gg</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>25</v>
+      </c>
+      <c r="E6" t="n">
+        <v>75</v>
+      </c>
+      <c r="F6" t="n">
+        <v>180</v>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Costa</t>
+        </is>
+      </c>
+      <c r="H6" t="n">
+        <v>50</v>
+      </c>
+      <c r="I6" t="n">
+        <v>1</v>
+      </c>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>Equilibrada</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>wawa</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>25</v>
+      </c>
+      <c r="E7" t="n">
+        <v>85</v>
+      </c>
+      <c r="F7" t="n">
+        <v>169</v>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Costa</t>
+        </is>
+      </c>
+      <c r="H7" t="n">
+        <v>50</v>
+      </c>
+      <c r="I7" t="n">
+        <v>4</v>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>2,3,6</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Equilibrada</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -6013,7 +6195,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I12"/>
+  <dimension ref="A1:I13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6447,6 +6629,41 @@
         <v>10</v>
       </c>
       <c r="I12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" t="n">
+        <v>4</v>
+      </c>
+      <c r="C13" t="n">
+        <v>31</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>snack</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>principal</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Ensalada de Atún</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="H13" t="n">
+        <v>10</v>
+      </c>
+      <c r="I13" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Database_ChefIA.xlsx
+++ b/Database_ChefIA.xlsx
@@ -418,7 +418,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M7"/>
+  <dimension ref="A1:M8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -569,7 +569,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>3,9,12,1</t>
+          <t>3,5,9</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -579,7 +579,7 @@
       </c>
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="n">
-        <v>34</v>
+        <v>10</v>
       </c>
     </row>
     <row r="4">
@@ -759,6 +759,55 @@
       </c>
       <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>keiko</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>25</v>
+      </c>
+      <c r="E8" t="n">
+        <v>86</v>
+      </c>
+      <c r="F8" t="n">
+        <v>163</v>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Costa</t>
+        </is>
+      </c>
+      <c r="H8" t="n">
+        <v>100</v>
+      </c>
+      <c r="I8" t="n">
+        <v>6</v>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>1,2,9,16,11</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>Equilibrada</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="n">
+        <v>32</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -6195,7 +6244,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I13"/>
+  <dimension ref="A1:I24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6664,6 +6713,391 @@
         <v>10</v>
       </c>
       <c r="I13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" t="n">
+        <v>2</v>
+      </c>
+      <c r="C14" t="n">
+        <v>23</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>desayuno</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>secundario</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Camote Sancochado con Huevo</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="H14" t="n">
+        <v>10</v>
+      </c>
+      <c r="I14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" t="n">
+        <v>2</v>
+      </c>
+      <c r="C15" t="n">
+        <v>2</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>almuerzo</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>principal</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Arroz con Pollo</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="H15" t="n">
+        <v>10</v>
+      </c>
+      <c r="I15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" t="n">
+        <v>2</v>
+      </c>
+      <c r="C16" t="n">
+        <v>10</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>cena</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>principal</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Aguadito de Pollo</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="H16" t="n">
+        <v>10</v>
+      </c>
+      <c r="I16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" t="n">
+        <v>7</v>
+      </c>
+      <c r="C17" t="n">
+        <v>29</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>desayuno</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>principal</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Ensalada de Camote y Pollo</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="H17" t="n">
+        <v>10</v>
+      </c>
+      <c r="I17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" t="n">
+        <v>7</v>
+      </c>
+      <c r="C18" t="n">
+        <v>14</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>almuerzo</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>secundario</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Pollo al Kion</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="H18" t="n">
+        <v>10</v>
+      </c>
+      <c r="I18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" t="n">
+        <v>7</v>
+      </c>
+      <c r="C19" t="n">
+        <v>15</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>cena</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>secundario</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Camote con Pavo</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="H19" t="n">
+        <v>10</v>
+      </c>
+      <c r="I19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" t="n">
+        <v>7</v>
+      </c>
+      <c r="C20" t="n">
+        <v>36</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>snack</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>principal</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Uvas con Queso</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="H20" t="n">
+        <v>10</v>
+      </c>
+      <c r="I20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" t="n">
+        <v>7</v>
+      </c>
+      <c r="C21" t="n">
+        <v>49</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>desayuno</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>secundario</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Tostadas con Mantequilla</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="H21" t="n">
+        <v>10</v>
+      </c>
+      <c r="I21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>21</v>
+      </c>
+      <c r="B22" t="n">
+        <v>7</v>
+      </c>
+      <c r="C22" t="n">
+        <v>2</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>almuerzo</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>principal</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Arroz con Pollo</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="H22" t="n">
+        <v>10</v>
+      </c>
+      <c r="I22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>22</v>
+      </c>
+      <c r="B23" t="n">
+        <v>7</v>
+      </c>
+      <c r="C23" t="n">
+        <v>7</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>cena</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>secundario</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Saltado de Tofu</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="H23" t="n">
+        <v>10</v>
+      </c>
+      <c r="I23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>23</v>
+      </c>
+      <c r="B24" t="n">
+        <v>7</v>
+      </c>
+      <c r="C24" t="n">
+        <v>32</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>snack</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>secundario</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Yogurt con Frutas</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="H24" t="n">
+        <v>10</v>
+      </c>
+      <c r="I24" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
